--- a/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.25%2385</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.01%13865</t>
+          <t>-2.99%13450</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>13865</v>
+        <v>13450</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.52%80,000</t>
+          <t>5.54%80,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>5.54%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.93%4275</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4275</v>
+        <v>4340</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.24%249,000</t>
+          <t>5.31%249,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.31%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.88%3395</t>
+          <t>-8.1%3120</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3395</v>
+        <v>3120</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.82%228,600</t>
+          <t>3.87%228,600</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.46%5445</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5445</v>
+        <v>5290</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.74%136,000</t>
+          <t>3.70%136,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1730</v>
+        <v>1760</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.68%404,000</t>
+          <t>3.49%404,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>1303南亞塑膠工業</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0%518</t>
+          <t>-6.95%221</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-6.95%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>518</v>
+        <v>221</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.77%1,096,000</t>
+          <t>2.86%2,416,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1096000</v>
+        <v>2416000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1303南亞塑膠工業</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.28%237.5</t>
+          <t>-7.82%477.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-7.82%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>237.5</v>
+        <v>477.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.76%2,416,000</t>
+          <t>2.83%1,096,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2416000</v>
+        <v>1096000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.21%973</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>973</v>
+        <v>923</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.67%563,000</t>
+          <t>2.73%563,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.95%251</t>
+          <t>-1.39%247.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>251</v>
+        <v>247.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.40%1,921,000</t>
+          <t>2.41%1,921,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.08%1175</t>
+          <t>-6.38%1100</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.08%</t>
+          <t>-6.38%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1175</v>
+        <v>1100</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.35%393,000</t>
+          <t>2.31%393,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3310</v>
+        <v>3300</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.23%134,000</t>
+          <t>2.21%134,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.73%5710</t>
+          <t>+2.8%5870</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.73%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5710</v>
+        <v>5870</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.09%73,000</t>
+          <t>2.08%73,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.82%2065</t>
+          <t>-5.59%169</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>-5.59%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2065</v>
+        <v>169</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.04%197,000</t>
+          <t>2.05%2,293,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>197000</v>
+        <v>2293000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:44</t>
+          <t>2026-09-03 21:25:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6669緯穎科技服務</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0%2610</t>
+          <t>-3.15%2000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2610</v>
+        <v>2000</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.98%52,000</t>
+          <t>2.03%197,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>52000</v>
+        <v>197000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>6669緯穎科技服務</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.95%5770</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-5.17%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5770</v>
+        <v>2475</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.98%69,000</t>
+          <t>2.02%155,105</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>69000</v>
+        <v>155105</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.7%179</t>
+          <t>-2.69%5615</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>179</v>
+        <v>5615</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.97%2,293,000</t>
+          <t>1.99%69,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2293000</v>
+        <v>69000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>6515穎崴科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.22%5290</t>
+          <t>-0.71%7000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5290</v>
+        <v>7000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.90%72,000</t>
+          <t>1.94%55,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>72000</v>
+        <v>55000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2140</v>
+        <v>5045</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.87%174,000</t>
+          <t>1.90%72,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>174000</v>
+        <v>72000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6515穎崴科技</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.03%7050</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7050</v>
+        <v>2090</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.85%55,000</t>
+          <t>1.86%174,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>55000</v>
+        <v>174000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.67%5895</t>
+          <t>-1.61%5800</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5895</v>
+        <v>5800</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.73%59,000</t>
+          <t>1.74%59,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>2382廣達電腦</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.93%540</t>
+          <t>-0.59%335</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.93%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>540</v>
+        <v>335</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.65%595,000</t>
+          <t>1.66%987,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>595000</v>
+        <v>987000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2382廣達電腦</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.46%337</t>
+          <t>+0.71%17850</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>337</v>
+        <v>17850</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.65%987,000</t>
+          <t>1.62%18,300</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>987000</v>
+        <v>18300</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3711日月光投資控股</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>-5.37%511</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>-5.37%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>589</v>
+        <v>511</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.57%526,000</t>
+          <t>1.60%595,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>526000</v>
+        <v>595000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.53%17725</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>17725</v>
+        <v>589</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.53%18,300</t>
+          <t>1.55%526,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>18300</v>
+        <v>526000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.76%1410</t>
+          <t>+1.35%67.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1410</v>
+        <v>67.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.48%209,000</t>
+          <t>1.50%4,525,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>209000</v>
+        <v>4525000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,25 +2090,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.71%1975</t>
+          <t>-4.61%1345</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1975</v>
+        <v>1345</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.47%148,000</t>
+          <t>1.47%209,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>148000</v>
+        <v>209000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2891中國信託金融控股</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.15%66.6</t>
+          <t>+2.03%2015</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>66.59999999999999</v>
+        <v>2015</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.47%4,525,000</t>
+          <t>1.46%148,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>4525000</v>
+        <v>148000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.55%536</t>
+          <t>-4.48%512</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:45</t>
+          <t>2026-09-03 21:25:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.5%40.5</t>
+          <t>+6.67%43.2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>+6.67%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>40.5</v>
+        <v>43.2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.23%6,340,622</t>
+          <t>1.28%6,340,622</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.7%361.5</t>
+          <t>-3.04%350.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>361.5</v>
+        <v>350.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.22%694,000</t>
+          <t>1.25%694,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.21%203,000</t>
+          <t>1.22%203,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-5.23%507</t>
+          <t>-8.48%464</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-8.48%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.20%461,000</t>
+          <t>1.17%461,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.14%73.4</t>
+          <t>-3.81%70.6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-3.81%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>73.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.12%3,124,500</t>
+          <t>1.14%3,124,500</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.59%187</t>
+          <t>-6.32%1185</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.59%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>187</v>
+        <v>1185</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.10%1,147,000</t>
+          <t>1.14%181,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1147000</v>
+        <v>181000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+7.66%1265</t>
+          <t>+1.87%190.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1265</v>
+        <v>190.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.04%181,000</t>
+          <t>1.07%1,147,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>181000</v>
+        <v>1147000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+3.03%7810</t>
+          <t>-8.45%7150</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>-8.45%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7810</v>
+        <v>7150</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.96%26,000</t>
+          <t>1.01%26,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8210勤誠興業</t>
+          <t>3231緯創資通</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.22%968</t>
+          <t>+1.62%188.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>968</v>
+        <v>188.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.93%193,000</t>
+          <t>0.96%1,041,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>193000</v>
+        <v>1041000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3231緯創資通</t>
+          <t>8210勤誠興業</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.92%185.5</t>
+          <t>-2.07%948</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>185.5</v>
+        <v>948</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.92%1,041,000</t>
+          <t>0.93%193,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1041000</v>
+        <v>193000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.42%708</t>
+          <t>-0.71%703</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.87%252,000</t>
+          <t>0.89%252,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.2%502</t>
+          <t>-2.89%487.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>502</v>
+        <v>487.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.85%345,000</t>
+          <t>0.86%345,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.09%847</t>
+          <t>-8.5%775</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>847</v>
+        <v>775</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.79%185,000</t>
+          <t>0.78%185,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.68%233.5</t>
+          <t>-3.21%226</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>233.5</v>
+        <v>226</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.75%650,000</t>
+          <t>0.76%650,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-7.66%2110</t>
+          <t>-0.71%2095</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-7.66%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2110</v>
+        <v>2095</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.60%54,000</t>
+          <t>0.57%54,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:46</t>
+          <t>2026-09-03 21:25:08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3529力旺電子</t>
+          <t>6831邁科科技</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-9.28%2395</t>
+          <t>-3.94%585</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-9.28%</t>
+          <t>-3.94%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2395</v>
+        <v>585</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.57%44,000</t>
+          <t>0.55%182,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>44000</v>
+        <v>182000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:48</t>
+          <t>2026-09-03 21:25:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6831邁科科技</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0%609</t>
+          <t>-2.71%2330</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>609</v>
+        <v>2330</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.54%182,000</t>
+          <t>0.53%44,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>182000</v>
+        <v>44000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:48</t>
+          <t>2026-09-03 21:25:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-6.16%686</t>
+          <t>-7%638</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-6.16%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>686</v>
+        <v>638</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.48%134,000</t>
+          <t>0.46%134,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:48</t>
+          <t>2026-09-03 21:25:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2170</v>
+        <v>2100</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.37%32,336</t>
+          <t>0.35%32,336</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:48</t>
+          <t>2026-09-03 21:25:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3533嘉澤端子工業</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.29%1705</t>
+          <t>-1.39%1770</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.29%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1705</v>
+        <v>1770</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.30%35,000</t>
+          <t>0.34%38,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:48</t>
+          <t>2026-09-03 21:25:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,25 +3493,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>3533嘉澤端子工業</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+9.79%1795</t>
+          <t>-2.05%1670</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+9.79%</t>
+          <t>-2.05%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1795</v>
+        <v>1670</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.30%38,000</t>
+          <t>0.30%35,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3520,11 +3520,11 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:06</t>
+          <t>2026-09-03 21:39:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:07</t>
+          <t>2026-09-03 21:39:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:08</t>
+          <t>2026-09-03 21:39:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:09</t>
+          <t>2026-09-03 21:39:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:09</t>
+          <t>2026-09-03 21:39:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:09</t>
+          <t>2026-09-03 21:39:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:09</t>
+          <t>2026-09-03 21:39:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:09</t>
+          <t>2026-09-03 21:39:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:47</t>
+          <t>2026-09-03 21:55:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:49</t>
+          <t>2026-09-03 21:55:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:50</t>
+          <t>2026-09-03 21:55:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:51</t>
+          <t>2026-09-03 21:55:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:51</t>
+          <t>2026-09-03 21:55:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:51</t>
+          <t>2026-09-03 21:55:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:51</t>
+          <t>2026-09-03 21:55:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:51</t>
+          <t>2026-09-03 21:55:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:41</t>
+          <t>2026-09-03 22:31:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:42</t>
+          <t>2026-09-03 22:31:06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:43</t>
+          <t>2026-09-03 22:31:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:45</t>
+          <t>2026-09-03 22:31:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:45</t>
+          <t>2026-09-03 22:31:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:45</t>
+          <t>2026-09-03 22:31:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:45</t>
+          <t>2026-09-03 22:31:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:45</t>
+          <t>2026-09-03 22:31:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:05</t>
+          <t>2026-09-03 22:44:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:06</t>
+          <t>2026-09-03 22:44:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:07</t>
+          <t>2026-09-03 22:44:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:09</t>
+          <t>2026-09-03 22:44:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:09</t>
+          <t>2026-09-03 22:44:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:09</t>
+          <t>2026-09-03 22:44:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:09</t>
+          <t>2026-09-03 22:44:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:31:09</t>
+          <t>2026-09-03 22:44:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:21</t>
+          <t>2026-09-03 23:00:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:22</t>
+          <t>2026-09-03 23:00:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:24</t>
+          <t>2026-09-03 23:00:06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:25</t>
+          <t>2026-09-03 23:00:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:25</t>
+          <t>2026-09-03 23:00:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:25</t>
+          <t>2026-09-03 23:00:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:25</t>
+          <t>2026-09-03 23:00:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:25</t>
+          <t>2026-09-03 23:00:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
